--- a/output/laminas_comunales/comunal_o_ocup_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,217 +384,217 @@
         </is>
       </c>
       <c r="C2">
-        <v>43.2227608702158</v>
+        <v>61.0320666489094</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C3">
-        <v>42.2280630669055</v>
+        <v>59.8604368932039</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C4">
-        <v>40.6631418350168</v>
+        <v>59.5830000888652</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C5">
-        <v>40.146386364986</v>
+        <v>59.3319644931143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C6">
-        <v>39.156602008865</v>
+        <v>58.5400169331142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C7">
-        <v>38.8677513359313</v>
+        <v>58.2997216772368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C8">
-        <v>36.9128828252682</v>
+        <v>57.6433246589386</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C9">
-        <v>36.7650037751137</v>
+        <v>57.2195333829734</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C10">
-        <v>35.8290488431877</v>
+        <v>57.0566644133727</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C11">
-        <v>34.8454202216338</v>
+        <v>55.4136721423682</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C12">
-        <v>34.1900468021333</v>
+        <v>55.0181338608638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="C13">
-        <v>34.1511954992968</v>
+        <v>54.4280795715379</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C14">
-        <v>33.9614320041366</v>
+        <v>54.4271835321277</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C15">
-        <v>33.7015618821669</v>
+        <v>53.9825046040516</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C16">
-        <v>33.644597431766</v>
+        <v>53.7261014131338</v>
       </c>
     </row>
     <row r="17">
@@ -609,217 +609,3232 @@
         </is>
       </c>
       <c r="C17">
-        <v>33.6340439586197</v>
+        <v>52.9775740358127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C18">
-        <v>32.7466294746629</v>
+        <v>52.7838145503467</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C19">
-        <v>31.3372867517511</v>
+        <v>52.493665054135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C20">
-        <v>31.0600534889375</v>
+        <v>51.8054287116595</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C21">
-        <v>30.2207858400519</v>
+        <v>51.6068659031257</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C22">
-        <v>30.0680203726042</v>
+        <v>51.3148495401375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C23">
-        <v>29.9541890998394</v>
+        <v>51.2592192840439</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C24">
-        <v>29.7639266304348</v>
+        <v>51.2131115072292</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C25">
-        <v>29.4268406337372</v>
+        <v>50.3678822776711</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C26">
-        <v>27.386847950057</v>
+        <v>49.849115080336</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C27">
-        <v>26.6750602145829</v>
+        <v>48.7912735849057</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C28">
-        <v>25.2508432603219</v>
+        <v>48.6123417269271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C29">
-        <v>24.937369519833</v>
+        <v>48.3937673595214</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C30">
-        <v>21.9978459881529</v>
+        <v>48.3904933814681</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>48.1370989127552</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>47.8591241337562</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>47.6416507001801</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>46.2505348737698</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>46.1999725877193</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>45.9987593052109</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>45.9720534629405</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>45.9552295594825</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>45.8223148095301</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>45.6488213262833</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>45.3362724757953</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>45.078751330259</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>44.7322670375522</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>44.6611358758461</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>44.3369415048425</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>43.9133986928105</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>43.3603736479843</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>43.2227608702158</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>42.8880685443442</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>42.8851160636613</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>42.765935072934</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>42.6389200508563</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>42.5720090833035</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>42.520145921812</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>42.5136536147366</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>42.5043233895374</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>42.250506585613</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>42.2280630669055</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>42.193660903852</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>41.5443952076153</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>41.4435921519516</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>40.6631418350168</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>40.3116343490305</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>40.1924394700777</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>40.146386364986</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>39.8184615465675</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>39.743317776835</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>39.6600566572238</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>39.6387392085289</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>39.4868387749937</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>39.156602008865</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>39.1024691358025</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>38.9486211424819</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>38.8933948922719</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>38.8677513359313</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>38.7212196639701</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>38.6492151701277</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>38.6452098256632</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>38.4341739105488</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>37.9643962848297</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>37.7729677729678</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>37.5874972485142</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>37.4245169082126</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>37.2876557191393</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>37.1719811518206</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>36.9128828252682</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>36.7904678019182</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>36.7650037751137</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>36.6862193168455</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>36.6818873668189</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>36.6450863213811</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>36.469864698647</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>36.1561393702255</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>36.0302677532014</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>36.0294241066183</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>35.8290488431877</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>35.7738840216938</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>35.6995884773663</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>35.5321242282585</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>35.4445520723259</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>35.4190530736922</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>35.2842653436431</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>34.9363522986281</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>34.9163216011042</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>34.8454202216338</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>34.8347869247678</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>34.7069597069597</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>34.478313618441</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>34.4265676567657</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>34.2542878448919</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>34.1900468021333</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>34.1511954992968</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>34.0545558411882</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>34.0497831887925</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>33.9614320041366</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>33.8036422646953</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>33.7015618821669</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>33.6978489966797</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>33.644597431766</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>33.6340439586197</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>33.5951495108171</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>33.5561858454889</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>33.4825765032068</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>33.1367162249515</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>33.112212696576</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>33.0322025565388</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>32.7953834115806</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>32.7466294746629</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>32.6675398384632</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>32.6512726718488</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>32.3984526112186</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>32.3594266813671</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>32.2860525886004</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>32.2085530169889</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>32.125</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>31.8019301930193</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>31.7509296621568</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>31.3813947948306</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>31.3372867517511</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>31.0656362251007</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>31.0600534889375</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>31.0307743216413</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>10306</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>San Juan de la Costa</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C143">
+        <v>31.0213243546577</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>30.9167953525995</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>30.9134456557648</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>30.6545879157684</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>30.4253532950888</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>30.2207858400519</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>30.0680203726042</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>29.9541890998394</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>29.885877318117</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>29.7752808988764</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>29.7639266304348</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>29.4268406337372</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>29.3663502230356</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>29.1312559017941</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>28.9257944557133</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>28.1096402123337</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>28.1075930812079</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>28.0900900900901</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>27.9197234168142</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>27.6876040466129</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>27.6622646810902</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>27.386847950057</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>27.1850013785498</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>27.1366405570061</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>26.9197207678883</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>26.7997727457187</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>26.7930489731438</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>26.6750602145829</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>26.6259082048556</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>26.5573432343234</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>26.3205055649877</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>26.2983253162302</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>26.1630919075743</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>25.7403581267218</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>25.7328207592504</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>25.6660997732426</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>25.6362016941142</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>25.6224826071036</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>25.3174200101574</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>25.317396002161</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>25.2508432603219</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>25.1576044129236</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>24.937369519833</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>24.6891651865009</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>24.1976157725814</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>24.0595966462724</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>23.9933833615751</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>23.3284927694076</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>22.6082435242957</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>22.5854440036619</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>22.5134059851237</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>21.9978459881529</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>19.3174032202809</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>19.1344058991118</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>18.2521489971347</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C198">
         <v>17.3878314847779</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>15.1861624157139</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>14.2052257201211</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>12.8364376810203</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>12.5962463907603</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>12.0926143024619</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>11.8883312421581</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>11.4050337906854</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>11.0406939551049</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>11.0303617571059</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>10.5927573558105</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>10.4852968971972</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>10.3142734768176</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>10.2179487179487</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>10.0003187352585</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>9.71012895403946</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>9.619920660448161</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>9.253284357523411</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>8.28637295081967</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>8.22294476557482</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>8.08973123460756</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>7.77101769911504</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>7.64992035817297</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>7.59081030735796</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>7.55047912388775</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>7.53054101221641</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>7.19277426160338</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>7.03531901041667</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>6.54372860255213</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>5.88503649635036</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>5.69212592423203</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>5.55555555555556</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>5.48744892002335</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>5.41666666666667</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>3.2032032032032</v>
       </c>
     </row>
   </sheetData>
